--- a/EXCEL/Homework/VLOOKUP_LAB.xlsx
+++ b/EXCEL/Homework/VLOOKUP_LAB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANUDIP_BY_SAYAR_DPBA\EXCEL\Homework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBEE6332-1970-4EEA-8CEC-D95012E43081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294D6480-01F6-4B3D-A065-9E39AEA4EE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{63CCB0DF-6991-42B9-9F00-F78D229B06A3}"/>
   </bookViews>
@@ -219,6 +219,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -228,7 +229,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -941,12 +941,12 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -1025,21 +1025,21 @@
       <c r="D16" s="4"/>
     </row>
     <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
@@ -1173,13 +1173,13 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -1244,13 +1244,13 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
@@ -1396,13 +1396,13 @@
       </c>
     </row>
     <row r="46" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
@@ -1547,13 +1547,13 @@
       </c>
     </row>
     <row r="57" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
@@ -1637,13 +1637,13 @@
       <c r="C65" s="9"/>
     </row>
     <row r="66" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
@@ -1655,7 +1655,7 @@
       <c r="C67" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D67" s="13"/>
+      <c r="D67" s="10"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
